--- a/04_STATISTICAL_ANALYSES/04_REVIEWER_WORKBOOKS/master_results_tables.xlsx
+++ b/04_STATISTICAL_ANALYSES/04_REVIEWER_WORKBOOKS/master_results_tables.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra43eba0c32384dac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confirmatory" sheetId="2" r:id="R4e8db35d5a9a4b4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset effects" sheetId="3" r:id="Ra2de39a5e47e4c23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model effects" sheetId="4" r:id="R22124111a15c4037"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregation" sheetId="5" r:id="Rcd0dda44e0e9434a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample size" sheetId="6" r:id="Rcf015a118dd3431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completion" sheetId="7" r:id="R6dd50a9218f74ef8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset map" sheetId="8" r:id="Rc7d34fbc247d4e04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric warnings" sheetId="9" r:id="R13787e43afe0409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R75504056dc804d3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confirmatory" sheetId="2" r:id="R7255d4ca5d964c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset effects" sheetId="3" r:id="Rafbc1f1b03174182"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model effects" sheetId="4" r:id="R97c037d7a04140fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aggregation" sheetId="5" r:id="R12f5fdf6be604a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample size" sheetId="6" r:id="R4b14390f6b5f452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Completion" sheetId="7" r:id="R5c6d01a0bb1d4810"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dataset map" sheetId="8" r:id="R37af401fe64246ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric warnings" sheetId="9" r:id="Raedab4cf343044d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3394,10 +3394,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.110000133514404" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.559999942779541" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16.219999313354492" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
@@ -3427,10 +3427,10 @@
         <x:v>C2</x:v>
       </x:c>
       <x:c r="C4" s="28" t="n">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="29" t="n">
-        <x:v>0.0013967297592376582</x:v>
+        <x:v>0.00222884637168</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3441,10 +3441,10 @@
         <x:v>C3</x:v>
       </x:c>
       <x:c r="C5" s="28" t="n">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="29" t="n">
-        <x:v>-0.0002578485607608316</x:v>
+        <x:v>0.00008467858662380009</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3455,10 +3455,10 @@
         <x:v>C4</x:v>
       </x:c>
       <x:c r="C6" s="28" t="n">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D6" s="29" t="n">
-        <x:v>0.00014941934474343999</x:v>
+        <x:v>-0.0009937238143015</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3469,10 +3469,10 @@
         <x:v>C5</x:v>
       </x:c>
       <x:c r="C7" s="28" t="n">
-        <x:v>21</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="29" t="n">
-        <x:v>0.014405734713667906</x:v>
+        <x:v>0.0127263639762366</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3483,10 +3483,10 @@
         <x:v>C2</x:v>
       </x:c>
       <x:c r="C8" s="28" t="n">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="29" t="n">
-        <x:v>0.0064601728368473</x:v>
+        <x:v>0.0053216724754673</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3497,10 +3497,10 @@
         <x:v>C3</x:v>
       </x:c>
       <x:c r="C9" s="28" t="n">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="29" t="n">
-        <x:v>0.0005521253415324834</x:v>
+        <x:v>-0.0009787354246117</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3511,10 +3511,10 @@
         <x:v>C4</x:v>
       </x:c>
       <x:c r="C10" s="28" t="n">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D10" s="29" t="n">
-        <x:v>0.00044312169312166194</x:v>
+        <x:v>0.0003114001067201</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -3525,10 +3525,10 @@
         <x:v>C5</x:v>
       </x:c>
       <x:c r="C11" s="28" t="n">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D11" s="29" t="n">
-        <x:v>0.02445639912827602</x:v>
+        <x:v>0.0249170907134619</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3542,7 +3542,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D12" s="29" t="n">
-        <x:v>0.0042571592114257015</x:v>
+        <x:v>0.0042571592114256</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3556,7 +3556,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="29" t="n">
-        <x:v>-0.0008853982333427157</x:v>
+        <x:v>-0.0008853982333427</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3570,7 +3570,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D14" s="29" t="n">
-        <x:v>-0.00018649212228660783</x:v>
+        <x:v>-0.0001864921222865</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -3584,7 +3584,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D15" s="29" t="n">
-        <x:v>0.022572046440147674</x:v>
+        <x:v>0.0225720464401476</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
